--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -808,718 +808,718 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9882,0.0012,0.0020,0.0017</t>
-  </si>
-  <si>
-    <t>0.0004,0.0048,0.0000,0.9993</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.1415,0.0009,0.0000,0.9171</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0018,0.0002,0.0002</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9432,0.0053,0.0104,0.0126</t>
+  </si>
+  <si>
+    <t>0.0001,0.0101,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.1252,0.0007,0.0000,0.9575</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0006,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9984,0.0014,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9961,0.0033,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9886,0.0004,0.0052,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0688,0.0005,0.9557,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.9988,0.0004</t>
+  </si>
+  <si>
+    <t>0.9988,0.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.9974,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9971,0.0001,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9491,0.0002,0.0561,0.0007</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.0007,0.9979,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9133,0.0467,0.0026,0.0004</t>
+  </si>
+  <si>
+    <t>0.3351,0.2026,0.1249,0.0019</t>
+  </si>
+  <si>
+    <t>0.0005,0.0006,0.9990,0.0052</t>
+  </si>
+  <si>
+    <t>0.0095,0.9735,0.0164,0.0001</t>
+  </si>
+  <si>
+    <t>0.9823,0.0067,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.9925,0.0014,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.9320,0.0652,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.9912,0.2810,0.0000</t>
+  </si>
+  <si>
+    <t>0.1254,0.0606,0.1492,0.0127</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.0073,0.9960,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.9925,0.0051</t>
+  </si>
+  <si>
+    <t>0.0000,0.0051,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9989,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0108,0.0456,0.0352,0.8766</t>
+  </si>
+  <si>
+    <t>0.0002,0.9979,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.0001,0.9983,0.0352,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0021,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0135,0.0037,0.9836,0.0005</t>
+  </si>
+  <si>
+    <t>0.0030,0.0004,0.9964,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0025,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0060,0.9974,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0007,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9855,0.0085,0.0046,0.0029</t>
+  </si>
+  <si>
+    <t>0.0020,0.0014,0.9982,0.0009</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9952,0.0021,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9984,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0046,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.0046,0.0067,0.9873,0.0017</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.9877,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0080,0.9882,0.0032,0.0009</t>
+  </si>
+  <si>
+    <t>0.0002,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9929,0.0002,0.0033,0.0002</t>
+  </si>
+  <si>
+    <t>0.0575,0.0016,0.9478,0.0008</t>
+  </si>
+  <si>
+    <t>0.0004,0.0006,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9968,0.9162,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9855,0.7856,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.0259,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9981,0.9887,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0019,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0011,0.9999</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9967,0.5247,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9681,0.9961,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.7421,0.6156,0.0012</t>
+  </si>
+  <si>
+    <t>0.0000,0.2773,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9822,0.9787,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9526,0.9772,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0007,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9989,0.0010,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0013,0.0002,0.0003</t>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0007,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9962,0.0014,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.9979,0.0024,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.0293,0.0009,0.9750,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9990,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9976,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.9951,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.6237,0.4693,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.2518,0.0129,0.5120,0.0025</t>
+  </si>
+  <si>
+    <t>0.7058,0.0010,0.3761,0.0002</t>
+  </si>
+  <si>
+    <t>0.6990,0.0050,0.2224,0.0018</t>
+  </si>
+  <si>
+    <t>0.8646,0.0095,0.0269,0.0099</t>
+  </si>
+  <si>
+    <t>0.0004,0.0053,0.0044,0.9814</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9809,0.9966,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9988,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9015,0.0846,0.0046,0.0004</t>
+  </si>
+  <si>
+    <t>0.8464,0.1392,0.0039,0.0004</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9979,0.0014,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9851,0.0003,0.0113,0.0001</t>
-  </si>
-  <si>
-    <t>0.0107,0.0003,0.9877,0.0016</t>
-  </si>
-  <si>
-    <t>0.0402,0.0002,0.9808,0.0000</t>
-  </si>
-  <si>
-    <t>0.0041,0.0005,0.9946,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0189,0.9800,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9988,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.8455,0.0005,0.2039,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.1706,0.0002,0.8960,0.0000</t>
-  </si>
-  <si>
-    <t>0.0074,0.0001,0.9936,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9998,0.0004</t>
-  </si>
-  <si>
-    <t>0.4001,0.5998,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.6476,0.0371,0.1267,0.0022</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.9999,0.0087</t>
-  </si>
-  <si>
-    <t>0.0069,0.9419,0.0702,0.0002</t>
-  </si>
-  <si>
-    <t>0.9869,0.0026,0.0022,0.0002</t>
-  </si>
-  <si>
-    <t>0.9937,0.0010,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.5902,0.4054,0.0007,0.0010</t>
-  </si>
-  <si>
-    <t>0.0013,0.9901,0.0761,0.0000</t>
-  </si>
-  <si>
-    <t>0.0689,0.1646,0.2485,0.0053</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.0062,0.9943,0.0003</t>
-  </si>
-  <si>
-    <t>0.0377,0.0000,0.8213,0.0013</t>
-  </si>
-  <si>
-    <t>0.0000,0.0150,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9982,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.3685,0.0210,0.7915</t>
-  </si>
-  <si>
-    <t>0.0001,0.9989,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9985,0.3201,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0002,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0050,0.9976,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0005,0.9984,0.0004</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0032,0.0007,0.9947,0.0009</t>
-  </si>
-  <si>
-    <t>0.9990,0.0009,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0021,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0008,0.9993,0.0021</t>
-  </si>
-  <si>
-    <t>0.9985,0.0003,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9986,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9991,0.9876,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0012,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0374,0.0023,0.9432,0.0023</t>
-  </si>
-  <si>
-    <t>0.0000,0.9932,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0125,0.9879,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9948,0.0004,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.7544,0.0028,0.1453,0.0010</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9998,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.8865,0.9898,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9309,0.9560,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9993,0.0088,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.8158,0.0000</t>
-  </si>
-  <si>
-    <t>0.0024,0.0001,0.0004,0.9989</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.9168,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9783,0.9854,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9887,0.0353,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.9158,0.9765,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9978,0.9963,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.6180,0.9914,0.0000</t>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0001,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0007,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0846,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.2916,0.9969,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0041,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0060,0.0014,0.9915,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9100,0.0018,0.0711,0.0006</t>
+  </si>
+  <si>
+    <t>0.0045,0.0001,0.9976,0.0000</t>
+  </si>
+  <si>
+    <t>0.5029,0.0052,0.4759,0.0012</t>
+  </si>
+  <si>
+    <t>0.0641,0.0007,0.0003,0.9789</t>
+  </si>
+  <si>
+    <t>0.0003,0.9830,0.4982,0.0002</t>
+  </si>
+  <si>
+    <t>0.9942,0.0031,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.0105,0.9807,0.0042,0.0028</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0300,0.9678,0.0023,0.0016</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0056,0.0001,0.0000,0.9984</t>
+  </si>
+  <si>
+    <t>0.0005,0.0045,0.9969,0.0169</t>
+  </si>
+  <si>
+    <t>0.9422,0.0001,0.0096,0.0117</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.1844,0.8229,0.0045,0.0006</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0810,0.8918,0.0088,0.0010</t>
+  </si>
+  <si>
+    <t>0.9954,0.0009,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9982,0.0004,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.8628,0.0841,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9385,0.0624,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.5984,0.4553,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.4169,0.0864,0.2392,0.0004</t>
+  </si>
+  <si>
+    <t>0.8203,0.2065,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9908,0.0013,0.0026,0.0013</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9883,0.0097,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9780,0.0079,0.0066,0.0020</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0230,0.9990,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0202,0.9938,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0024,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0014,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0010,0.9978,0.0002</t>
+  </si>
+  <si>
+    <t>0.0766,0.0012,0.9123,0.0016</t>
+  </si>
+  <si>
+    <t>0.0201,0.0073,0.9648,0.0006</t>
+  </si>
+  <si>
+    <t>0.0098,0.0206,0.9594,0.0004</t>
+  </si>
+  <si>
+    <t>0.0229,0.0094,0.9509,0.0009</t>
+  </si>
+  <si>
+    <t>0.5608,0.0047,0.4167,0.0005</t>
+  </si>
+  <si>
+    <t>0.8848,0.0017,0.0613,0.0050</t>
+  </si>
+  <si>
+    <t>0.8556,0.0037,0.0988,0.0007</t>
+  </si>
+  <si>
+    <t>0.0258,0.9787,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0057,0.9935,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.6994,0.4030,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9775,0.0177,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.0061,0.9930,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9959,0.0005,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9721,0.0006,0.0182,0.0004</t>
+  </si>
+  <si>
+    <t>0.9762,0.0021,0.0042,0.0005</t>
+  </si>
+  <si>
+    <t>0.9817,0.0018,0.0036,0.0002</t>
+  </si>
+  <si>
+    <t>0.8156,0.0019,0.1323,0.0046</t>
+  </si>
+  <si>
+    <t>0.0007,0.0006,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0477,0.0012,0.9213,0.0020</t>
+  </si>
+  <si>
+    <t>0.0002,0.0046,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.9982,0.0008</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9962,0.0015,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9727,0.0223,0.0012,0.0016</t>
+  </si>
+  <si>
+    <t>0.9988,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9971,0.0021,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9951,0.0023,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9974,0.0010,0.0006,0.0010</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0017,0.9994,0.0013</t>
+  </si>
+  <si>
+    <t>0.2239,0.1382,0.2616,0.0020</t>
+  </si>
+  <si>
+    <t>0.5535,0.0003,0.2164,0.0151</t>
+  </si>
+  <si>
+    <t>0.0004,0.0004,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0024,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.2853,0.9256,0.0013</t>
+  </si>
+  <si>
+    <t>0.1682,0.0002,0.8893,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0365,0.0077,0.9529,0.0060</t>
+  </si>
+  <si>
+    <t>0.0093,0.0010,0.9788,0.0085</t>
+  </si>
+  <si>
+    <t>0.9903,0.0001,0.0042,0.0002</t>
+  </si>
+  <si>
+    <t>0.9587,0.0000,0.0362,0.0003</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9980,0.0019,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9998,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9989,0.0009,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0005,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9984,0.0002,0.0000,0.0010</t>
-  </si>
-  <si>
-    <t>0.9936,0.0036,0.0007,0.0015</t>
-  </si>
-  <si>
-    <t>0.9991,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0176,0.0083,0.9767,0.0003</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9991,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9982,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9990,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.3473,0.6781,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.1894,0.0096,0.7274,0.0016</t>
-  </si>
-  <si>
-    <t>0.7414,0.0027,0.1563,0.0016</t>
-  </si>
-  <si>
-    <t>0.9842,0.0023,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.2081,0.0049,0.6226,0.0298</t>
-  </si>
-  <si>
-    <t>0.0001,0.7919,0.0010,0.8178</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9763,0.9975,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9995,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.2907,0.6603,0.0132,0.0009</t>
-  </si>
-  <si>
-    <t>0.9542,0.0331,0.0036,0.0005</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9981,0.0003,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.3103,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.4072,0.9963,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0807,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0066,0.0057,0.9886,0.0002</t>
-  </si>
-  <si>
-    <t>0.9979,0.0000,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9593,0.0023,0.0153,0.0024</t>
-  </si>
-  <si>
-    <t>0.1052,0.0000,0.9423,0.0001</t>
-  </si>
-  <si>
-    <t>0.1490,0.0026,0.8664,0.0007</t>
-  </si>
-  <si>
-    <t>0.0057,0.0007,0.0001,0.9985</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9970,0.7986,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0023,0.9924,0.0013,0.0288</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.1209,0.8877,0.0019,0.0017</t>
-  </si>
-  <si>
-    <t>0.0190,0.0000,0.0000,0.9937</t>
-  </si>
-  <si>
-    <t>0.0003,0.0065,0.9982,0.0068</t>
-  </si>
-  <si>
-    <t>0.9522,0.0001,0.0050,0.0192</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.0233,0.9661,0.0053,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.1921,0.8216,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.9779,0.0033,0.0077,0.0014</t>
-  </si>
-  <si>
-    <t>0.9942,0.0007,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9157,0.0516,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9424,0.0511,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.5275,0.5117,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.4001,0.0419,0.4537,0.0061</t>
-  </si>
-  <si>
-    <t>0.7214,0.3486,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9964,0.0006,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9760,0.0209,0.0007,0.0012</t>
-  </si>
-  <si>
-    <t>0.0000,0.0025,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9650,0.0269,0.0034,0.0021</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0063,0.9970,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.0013,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0113,0.9954,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0015,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0221,0.0009,0.9759,0.0014</t>
-  </si>
-  <si>
-    <t>0.0034,0.0013,0.9941,0.0002</t>
-  </si>
-  <si>
-    <t>0.8142,0.0011,0.1610,0.0007</t>
-  </si>
-  <si>
-    <t>0.0180,0.0120,0.9503,0.0005</t>
-  </si>
-  <si>
-    <t>0.0090,0.0233,0.9709,0.0003</t>
-  </si>
-  <si>
-    <t>0.3657,0.0096,0.6578,0.0004</t>
-  </si>
-  <si>
-    <t>0.9903,0.0004,0.0036,0.0003</t>
-  </si>
-  <si>
-    <t>0.9484,0.0012,0.0417,0.0004</t>
-  </si>
-  <si>
-    <t>0.1243,0.9153,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.9992,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.7465,0.3101,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9629,0.0281,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.0057,0.9922,0.0004,0.0015</t>
-  </si>
-  <si>
-    <t>0.9947,0.0006,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0000,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.8427,0.0236,0.0193,0.0056</t>
-  </si>
-  <si>
-    <t>0.9848,0.0019,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.9449,0.0053,0.0186,0.0013</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0444,0.0181,0.8721,0.0048</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0650,0.0004,0.9360,0.0004</t>
-  </si>
-  <si>
-    <t>0.0050,0.0441,0.8358,0.0142</t>
-  </si>
-  <si>
-    <t>0.9985,0.0007,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9965,0.0016,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9622,0.0318,0.0047,0.0035</t>
-  </si>
-  <si>
-    <t>0.9956,0.0054,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9967,0.0028,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9911,0.0069,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9890,0.0023,0.0037,0.0041</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9999,0.0008</t>
-  </si>
-  <si>
-    <t>0.0131,0.0480,0.9642,0.0016</t>
-  </si>
-  <si>
-    <t>0.9559,0.0004,0.0093,0.0070</t>
-  </si>
-  <si>
-    <t>0.0079,0.0002,0.9943,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0009,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.7334,0.9325,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.5309,0.0004,0.5635,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0034,0.0014,0.9909,0.0015</t>
-  </si>
-  <si>
-    <t>0.9959,0.0001,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.8964,0.0000,0.1131,0.0002</t>
-  </si>
-  <si>
-    <t>0.9983,0.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0005,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0013,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0005,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9941,0.0046,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9978,0.0007,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.0025,0.0007,0.9963,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0019,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0017,0.9979,0.0012</t>
-  </si>
-  <si>
-    <t>0.0001,0.0055,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0063,0.0043,0.9851,0.0019</t>
-  </si>
-  <si>
-    <t>0.0074,0.0018,0.9836,0.0047</t>
-  </si>
-  <si>
-    <t>0.0012,0.0017,0.9969,0.0007</t>
-  </si>
-  <si>
-    <t>0.0054,0.0001,0.9940,0.0002</t>
-  </si>
-  <si>
-    <t>0.9940,0.0002,0.0000,0.0038</t>
-  </si>
-  <si>
-    <t>0.0001,0.0397,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.1049,0.0001,0.0016,0.9559</t>
-  </si>
-  <si>
-    <t>0.9061,0.0028,0.0373,0.0109</t>
+    <t>0.9953,0.0030,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9988,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0005,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9979,0.0006,0.0005,0.0010</t>
+  </si>
+  <si>
+    <t>0.0011,0.0014,0.9968,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0139,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0015,0.0017,0.9962,0.0006</t>
+  </si>
+  <si>
+    <t>0.0019,0.0246,0.9781,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.0009,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.0002,0.9967,0.0007</t>
+  </si>
+  <si>
+    <t>0.0364,0.0022,0.9551,0.0029</t>
+  </si>
+  <si>
+    <t>0.0071,0.0000,0.9760,0.0010</t>
+  </si>
+  <si>
+    <t>0.9787,0.0007,0.0005,0.0174</t>
+  </si>
+  <si>
+    <t>0.0002,0.0043,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0185,0.0001,0.0001,0.9961</t>
+  </si>
+  <si>
+    <t>0.9920,0.0004,0.0013,0.0009</t>
   </si>
 </sst>
 </file>
@@ -2185,7 +2185,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2199,7 +2199,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2213,7 +2213,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2227,7 +2227,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2241,7 +2241,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2255,7 +2255,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2269,7 +2269,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2283,7 +2283,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2297,7 +2297,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2308,10 +2308,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2322,10 +2322,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2339,7 +2339,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2353,7 +2353,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2367,7 +2367,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2381,7 +2381,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2395,7 +2395,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2409,7 +2409,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2420,10 +2420,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2437,7 +2437,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2451,7 +2451,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2465,7 +2465,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2479,7 +2479,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2493,7 +2493,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2507,7 +2507,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2521,7 +2521,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2535,7 +2535,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2549,7 +2549,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2563,7 +2563,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2577,7 +2577,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2591,7 +2591,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2605,7 +2605,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2619,7 +2619,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2633,7 +2633,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2647,7 +2647,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2661,7 +2661,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2675,7 +2675,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2689,7 +2689,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2703,7 +2703,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2717,7 +2717,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2731,7 +2731,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2745,7 +2745,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2759,7 +2759,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2773,7 +2773,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2787,7 +2787,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2801,7 +2801,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2815,7 +2815,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2829,7 +2829,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2843,7 +2843,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2857,7 +2857,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2868,10 +2868,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2885,7 +2885,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2899,7 +2899,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2913,7 +2913,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2927,7 +2927,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2941,7 +2941,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2955,7 +2955,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2969,7 +2969,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2983,7 +2983,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2997,7 +2997,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3011,7 +3011,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3025,7 +3025,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3039,7 +3039,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3053,7 +3053,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3064,10 +3064,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3078,10 +3078,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3095,7 +3095,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3109,7 +3109,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3123,7 +3123,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3137,7 +3137,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3151,7 +3151,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3165,7 +3165,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3179,7 +3179,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3193,7 +3193,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3207,7 +3207,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3221,7 +3221,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3235,7 +3235,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3249,7 +3249,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>357</v>
+        <v>272</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3263,7 +3263,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3305,7 +3305,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3319,7 +3319,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3333,7 +3333,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3347,7 +3347,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>361</v>
+        <v>330</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3484,7 +3484,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
         <v>371</v>
@@ -3540,7 +3540,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
         <v>375</v>
@@ -3554,7 +3554,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>376</v>
@@ -3638,7 +3638,7 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
         <v>382</v>
@@ -3669,7 +3669,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>272</v>
+        <v>360</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3876,7 +3876,7 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
         <v>398</v>
@@ -3907,7 +3907,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3921,7 +3921,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>400</v>
+        <v>341</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3935,7 +3935,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>401</v>
+        <v>341</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3946,10 +3946,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3963,7 +3963,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3977,7 +3977,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3991,7 +3991,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4005,7 +4005,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4019,7 +4019,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>390</v>
+        <v>405</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4033,7 +4033,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4047,7 +4047,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>275</v>
+        <v>384</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4061,7 +4061,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4075,7 +4075,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4089,7 +4089,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4103,7 +4103,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4117,7 +4117,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4131,7 +4131,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4145,7 +4145,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4159,7 +4159,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4173,7 +4173,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4187,7 +4187,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4201,7 +4201,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>275</v>
+        <v>384</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4215,7 +4215,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4229,7 +4229,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4243,7 +4243,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4257,7 +4257,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4271,7 +4271,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>351</v>
+        <v>420</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4285,7 +4285,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4299,7 +4299,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4313,7 +4313,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4324,10 +4324,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4338,10 +4338,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4355,7 +4355,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4369,7 +4369,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4383,7 +4383,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4397,7 +4397,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4411,7 +4411,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4425,7 +4425,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4439,7 +4439,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4453,7 +4453,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4467,7 +4467,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4481,7 +4481,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4495,7 +4495,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4509,7 +4509,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4523,7 +4523,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4537,7 +4537,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4551,7 +4551,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4562,10 +4562,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4579,7 +4579,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4593,7 +4593,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4604,10 +4604,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4621,7 +4621,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4635,7 +4635,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4649,7 +4649,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4663,7 +4663,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4677,7 +4677,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4691,7 +4691,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4705,7 +4705,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4719,7 +4719,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4733,7 +4733,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4747,7 +4747,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4761,7 +4761,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4775,7 +4775,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4789,7 +4789,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4803,7 +4803,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4817,7 +4817,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4831,7 +4831,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4845,7 +4845,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4859,7 +4859,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4873,7 +4873,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4887,7 +4887,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4901,7 +4901,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4915,7 +4915,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4929,7 +4929,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4943,7 +4943,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4957,7 +4957,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4971,7 +4971,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4982,10 +4982,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4999,7 +4999,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5013,7 +5013,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5027,7 +5027,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5038,10 +5038,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5055,7 +5055,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>475</v>
+        <v>293</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5083,7 +5083,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>431</v>
+        <v>477</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5097,7 +5097,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5111,7 +5111,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5125,7 +5125,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5139,7 +5139,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5153,7 +5153,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5167,7 +5167,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5181,7 +5181,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5195,7 +5195,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5209,7 +5209,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5223,7 +5223,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>486</v>
+        <v>275</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5433,7 +5433,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5447,7 +5447,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="256" spans="1:4">
